--- a/public/downloads/LOE Supplement Planner_V2.xlsx
+++ b/public/downloads/LOE Supplement Planner_V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katy/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3708B7-E19D-6246-A702-CE21798EDC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1D32D8-C5FA-2E42-BCBB-5E4EBA5B120C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16200" yWindow="660" windowWidth="29100" windowHeight="25160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2780" yWindow="660" windowWidth="29100" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOE Supplement Planner" sheetId="1" r:id="rId1"/>
@@ -234,7 +234,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">• Monthly FTE cells are editable and default to 100%.
 </t>
@@ -245,7 +244,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">• Update only months where appointment/FTE changes occur.
 </t>
@@ -256,7 +254,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">• Yellow indicates FTE below 100%; red indicates FTE above 100%.
 </t>
@@ -267,7 +264,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">• Monthly compensation calculations use each month’s FTE directly.
 </t>
@@ -346,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="56">
   <si>
     <t>PI Name</t>
   </si>
@@ -630,6 +626,42 @@
   <si>
     <t>Designed by Katherine A. Gruber / Level of Effort with Supplement v2.0</t>
   </si>
+  <si>
+    <t>Jul-26</t>
+  </si>
+  <si>
+    <t>Aug-26</t>
+  </si>
+  <si>
+    <t>Sep-26</t>
+  </si>
+  <si>
+    <t>Oct-26</t>
+  </si>
+  <si>
+    <t>Nov-26</t>
+  </si>
+  <si>
+    <t>Dec-26</t>
+  </si>
+  <si>
+    <t>Jan-27</t>
+  </si>
+  <si>
+    <t>Feb-27</t>
+  </si>
+  <si>
+    <t>Mar-27</t>
+  </si>
+  <si>
+    <t>Apr-27</t>
+  </si>
+  <si>
+    <t>May-27</t>
+  </si>
+  <si>
+    <t>Jun-27</t>
+  </si>
 </sst>
 </file>
 
@@ -641,7 +673,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,12 +791,6 @@
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Cambria"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1590,7 +1616,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1700,10 +1726,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1922,7 +1944,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="48">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1956,6 +1978,78 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2193,21 +2287,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2265,53 +2359,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2322,16 +2374,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2657,39 +2699,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
       <c r="E1" s="34"/>
       <c r="F1" s="34"/>
       <c r="G1" s="34"/>
-      <c r="H1" s="72" t="s">
+      <c r="H1" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
       <c r="AD1" s="34"/>
       <c r="AE1" s="34"/>
       <c r="AF1" s="34"/>
@@ -2699,36 +2741,36 @@
       <c r="A2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="77"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="76"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="G2" s="37"/>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
       <c r="AD2" s="37"/>
       <c r="AE2" s="37"/>
       <c r="AF2" s="37"/>
@@ -2738,34 +2780,34 @@
       <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="79"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="78"/>
       <c r="E3" s="37"/>
       <c r="F3" s="37"/>
       <c r="G3" s="37"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
+      <c r="V3" s="68"/>
+      <c r="W3" s="68"/>
+      <c r="X3" s="68"/>
+      <c r="Y3" s="68"/>
+      <c r="Z3" s="68"/>
+      <c r="AA3" s="68"/>
+      <c r="AB3" s="68"/>
+      <c r="AC3" s="68"/>
       <c r="AD3" s="37"/>
       <c r="AE3" s="37"/>
       <c r="AF3" s="37"/>
@@ -2775,34 +2817,34 @@
       <c r="A4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="81"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="80"/>
       <c r="E4" s="37"/>
       <c r="F4" s="37"/>
       <c r="G4" s="37"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
-      <c r="AB4" s="69"/>
-      <c r="AC4" s="69"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="68"/>
+      <c r="S4" s="68"/>
+      <c r="T4" s="68"/>
+      <c r="U4" s="68"/>
+      <c r="V4" s="68"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="68"/>
+      <c r="Z4" s="68"/>
+      <c r="AA4" s="68"/>
+      <c r="AB4" s="68"/>
+      <c r="AC4" s="68"/>
       <c r="AD4" s="37"/>
       <c r="AE4" s="37"/>
       <c r="AF4" s="37"/>
@@ -2812,37 +2854,37 @@
       <c r="A5" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="82">
+      <c r="B5" s="81">
         <f>($B$4/12)*$B$10</f>
         <v>0</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
       <c r="G5" s="37"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="69"/>
-      <c r="W5" s="69"/>
-      <c r="X5" s="69"/>
-      <c r="Y5" s="69"/>
-      <c r="Z5" s="69"/>
-      <c r="AA5" s="69"/>
-      <c r="AB5" s="69"/>
-      <c r="AC5" s="69"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
+      <c r="AA5" s="68"/>
+      <c r="AB5" s="68"/>
+      <c r="AC5" s="68"/>
       <c r="AD5" s="37"/>
       <c r="AE5" s="37"/>
       <c r="AF5" s="37"/>
@@ -2852,34 +2894,34 @@
       <c r="A6" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="81"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="80"/>
       <c r="E6" s="37"/>
       <c r="F6" s="37"/>
       <c r="G6" s="37"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="69"/>
-      <c r="Z6" s="69"/>
-      <c r="AA6" s="69"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="69"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="68"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="68"/>
+      <c r="AB6" s="68"/>
+      <c r="AC6" s="68"/>
       <c r="AD6" s="37"/>
       <c r="AE6" s="37"/>
       <c r="AF6" s="37"/>
@@ -2889,37 +2931,37 @@
       <c r="A7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="84">
+      <c r="B7" s="83">
         <f>IF($B$11="Yes",($B$6/12)*$B$10,$B$6/12)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="85"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="69"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="69"/>
-      <c r="X7" s="69"/>
-      <c r="Y7" s="69"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="69"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="69"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="68"/>
+      <c r="T7" s="68"/>
+      <c r="U7" s="68"/>
+      <c r="V7" s="68"/>
+      <c r="W7" s="68"/>
+      <c r="X7" s="68"/>
+      <c r="Y7" s="68"/>
+      <c r="Z7" s="68"/>
+      <c r="AA7" s="68"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="68"/>
       <c r="AD7" s="37"/>
       <c r="AE7" s="37"/>
       <c r="AF7" s="37"/>
@@ -2929,34 +2971,34 @@
       <c r="A8" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="87"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="86"/>
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="69"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="68"/>
+      <c r="V8" s="68"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+      <c r="Z8" s="68"/>
+      <c r="AA8" s="68"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="68"/>
       <c r="AD8" s="37"/>
       <c r="AE8" s="37"/>
       <c r="AF8" s="37"/>
@@ -2966,34 +3008,34 @@
       <c r="A9" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="89"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="88"/>
       <c r="E9" s="37"/>
       <c r="F9" s="37"/>
       <c r="G9" s="37"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="69"/>
-      <c r="V9" s="69"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68"/>
+      <c r="Q9" s="68"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="68"/>
+      <c r="T9" s="68"/>
+      <c r="U9" s="68"/>
+      <c r="V9" s="68"/>
+      <c r="W9" s="68"/>
+      <c r="X9" s="68"/>
+      <c r="Y9" s="68"/>
+      <c r="Z9" s="68"/>
+      <c r="AA9" s="68"/>
+      <c r="AB9" s="68"/>
+      <c r="AC9" s="68"/>
       <c r="AD9" s="37"/>
       <c r="AE9" s="37"/>
       <c r="AF9" s="37"/>
@@ -3003,37 +3045,37 @@
       <c r="A10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="119">
+      <c r="B10" s="118">
         <f>AVERAGE(G17,I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17,AC17)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="119"/>
-      <c r="D10" s="120"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="37"/>
       <c r="F10" s="37"/>
       <c r="G10" s="37"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="68"/>
+      <c r="U10" s="68"/>
+      <c r="V10" s="68"/>
+      <c r="W10" s="68"/>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="68"/>
+      <c r="Z10" s="68"/>
+      <c r="AA10" s="68"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="68"/>
       <c r="AD10" s="37"/>
       <c r="AE10" s="37"/>
       <c r="AF10" s="37"/>
@@ -3043,34 +3085,34 @@
       <c r="A11" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="65"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="37"/>
       <c r="F11" s="37"/>
       <c r="G11" s="37"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="69"/>
-      <c r="V11" s="69"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="69"/>
-      <c r="Y11" s="69"/>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="69"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="69"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="68"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="68"/>
+      <c r="Z11" s="68"/>
+      <c r="AA11" s="68"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="68"/>
       <c r="AD11" s="37"/>
       <c r="AE11" s="37"/>
       <c r="AF11" s="37"/>
@@ -3080,37 +3122,37 @@
       <c r="A12" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="90">
+      <c r="B12" s="89">
         <f>$B$5+$B$7</f>
         <v>0</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="92"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="91"/>
       <c r="E12" s="37"/>
       <c r="F12" s="37"/>
       <c r="G12" s="37"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="69"/>
-      <c r="X12" s="69"/>
-      <c r="Y12" s="69"/>
-      <c r="Z12" s="69"/>
-      <c r="AA12" s="69"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="69"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="68"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="68"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="68"/>
       <c r="AD12" s="37"/>
       <c r="AE12" s="37"/>
       <c r="AF12" s="37"/>
@@ -3120,197 +3162,197 @@
       <c r="A13" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="66">
+      <c r="B13" s="65">
         <f>$B$12*(1+$B$8)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
       <c r="E13" s="37"/>
       <c r="F13" s="37"/>
       <c r="G13" s="37"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69"/>
-      <c r="T13" s="69"/>
-      <c r="U13" s="69"/>
-      <c r="V13" s="69"/>
-      <c r="W13" s="69"/>
-      <c r="X13" s="69"/>
-      <c r="Y13" s="69"/>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="69"/>
-      <c r="AB13" s="69"/>
-      <c r="AC13" s="69"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="68"/>
+      <c r="U13" s="68"/>
+      <c r="V13" s="68"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="68"/>
+      <c r="Y13" s="68"/>
+      <c r="Z13" s="68"/>
+      <c r="AA13" s="68"/>
+      <c r="AB13" s="68"/>
+      <c r="AC13" s="68"/>
       <c r="AD13" s="37"/>
       <c r="AE13" s="37"/>
       <c r="AF13" s="37"/>
       <c r="AG13" s="38"/>
     </row>
     <row r="14" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="101"/>
-      <c r="B14" s="102"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
-      <c r="O14" s="102"/>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="102"/>
-      <c r="R14" s="102"/>
-      <c r="S14" s="102"/>
-      <c r="T14" s="102"/>
-      <c r="U14" s="102"/>
-      <c r="V14" s="102"/>
-      <c r="W14" s="102"/>
-      <c r="X14" s="102"/>
-      <c r="Y14" s="102"/>
-      <c r="Z14" s="102"/>
-      <c r="AA14" s="102"/>
-      <c r="AB14" s="102"/>
-      <c r="AC14" s="102"/>
-      <c r="AD14" s="102"/>
-      <c r="AE14" s="102"/>
-      <c r="AF14" s="102"/>
-      <c r="AG14" s="103"/>
+      <c r="A14" s="100"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="101"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="101"/>
+      <c r="AC14" s="101"/>
+      <c r="AD14" s="101"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="101"/>
+      <c r="AG14" s="102"/>
     </row>
     <row r="15" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
-      <c r="S15" s="74"/>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="74"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74"/>
-      <c r="AA15" s="74"/>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="74"/>
-      <c r="AD15" s="74"/>
-      <c r="AE15" s="74"/>
-      <c r="AF15" s="74"/>
-      <c r="AG15" s="98"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="73"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="73"/>
+      <c r="AG15" s="97"/>
     </row>
     <row r="16" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="121" t="s">
+      <c r="A16" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="125" t="s">
+      <c r="D16" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="133" t="s">
+      <c r="E16" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="99" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="99" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="100"/>
-      <c r="J16" s="99" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="100"/>
-      <c r="L16" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="100"/>
-      <c r="N16" s="99" t="s">
-        <v>13</v>
-      </c>
-      <c r="O16" s="100"/>
-      <c r="P16" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="100"/>
-      <c r="R16" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="S16" s="100"/>
-      <c r="T16" s="99" t="s">
-        <v>16</v>
-      </c>
-      <c r="U16" s="100"/>
-      <c r="V16" s="99" t="s">
-        <v>17</v>
-      </c>
-      <c r="W16" s="100"/>
-      <c r="X16" s="99" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y16" s="100"/>
-      <c r="Z16" s="99" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA16" s="100"/>
-      <c r="AB16" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC16" s="100"/>
-      <c r="AD16" s="104" t="s">
+      <c r="F16" s="98" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="99"/>
+      <c r="H16" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="99"/>
+      <c r="J16" s="98" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="99"/>
+      <c r="L16" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="99"/>
+      <c r="N16" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="O16" s="99"/>
+      <c r="P16" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="98" t="s">
+        <v>50</v>
+      </c>
+      <c r="S16" s="99"/>
+      <c r="T16" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="99"/>
+      <c r="V16" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="W16" s="99"/>
+      <c r="X16" s="98" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA16" s="99"/>
+      <c r="AB16" s="98" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC16" s="99"/>
+      <c r="AD16" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="AE16" s="104" t="s">
+      <c r="AE16" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="AF16" s="104" t="s">
+      <c r="AF16" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AG16" s="117" t="s">
+      <c r="AG16" s="116" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="129"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="127"/>
+      <c r="A17" s="128"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="126"/>
       <c r="F17" s="60" t="s">
         <v>34</v>
       </c>
@@ -3320,7 +3362,7 @@
       <c r="H17" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="62">
+      <c r="I17" s="61">
         <v>1</v>
       </c>
       <c r="J17" s="60" t="s">
@@ -3383,17 +3425,17 @@
       <c r="AC17" s="61">
         <v>1</v>
       </c>
-      <c r="AD17" s="105"/>
-      <c r="AE17" s="105"/>
-      <c r="AF17" s="105"/>
-      <c r="AG17" s="115"/>
+      <c r="AD17" s="104"/>
+      <c r="AE17" s="104"/>
+      <c r="AF17" s="104"/>
+      <c r="AG17" s="114"/>
     </row>
     <row r="18" spans="1:33" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="130"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="128"/>
+      <c r="A18" s="129"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="127"/>
       <c r="F18" s="13" t="s">
         <v>29</v>
       </c>
@@ -3466,10 +3508,10 @@
       <c r="AC18" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AD18" s="106"/>
-      <c r="AE18" s="106"/>
-      <c r="AF18" s="106"/>
-      <c r="AG18" s="116"/>
+      <c r="AD18" s="105"/>
+      <c r="AE18" s="105"/>
+      <c r="AF18" s="105"/>
+      <c r="AG18" s="115"/>
     </row>
     <row r="19" spans="1:33" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="44"/>
@@ -4717,13 +4759,13 @@
       </c>
     </row>
     <row r="34" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="93" t="s">
+      <c r="A34" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
       <c r="F34" s="15">
         <f>SUM(F19:F33)</f>
         <v>0</v>
@@ -4838,195 +4880,195 @@
       </c>
     </row>
     <row r="35" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="107"/>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="109"/>
-      <c r="O35" s="109"/>
-      <c r="P35" s="109"/>
-      <c r="Q35" s="109"/>
-      <c r="R35" s="109"/>
-      <c r="S35" s="109"/>
-      <c r="T35" s="109"/>
-      <c r="U35" s="109"/>
-      <c r="V35" s="109"/>
-      <c r="W35" s="109"/>
-      <c r="X35" s="109"/>
-      <c r="Y35" s="109"/>
-      <c r="Z35" s="109"/>
-      <c r="AA35" s="109"/>
-      <c r="AB35" s="109"/>
-      <c r="AC35" s="109"/>
-      <c r="AD35" s="109"/>
-      <c r="AE35" s="109"/>
-      <c r="AF35" s="109"/>
-      <c r="AG35" s="110"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="107"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="108"/>
+      <c r="S35" s="108"/>
+      <c r="T35" s="108"/>
+      <c r="U35" s="108"/>
+      <c r="V35" s="108"/>
+      <c r="W35" s="108"/>
+      <c r="X35" s="108"/>
+      <c r="Y35" s="108"/>
+      <c r="Z35" s="108"/>
+      <c r="AA35" s="108"/>
+      <c r="AB35" s="108"/>
+      <c r="AC35" s="108"/>
+      <c r="AD35" s="108"/>
+      <c r="AE35" s="108"/>
+      <c r="AF35" s="108"/>
+      <c r="AG35" s="109"/>
     </row>
     <row r="36" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="111"/>
-      <c r="B36" s="109"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="109"/>
-      <c r="E36" s="109"/>
-      <c r="F36" s="109"/>
-      <c r="G36" s="109"/>
-      <c r="H36" s="109"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="109"/>
-      <c r="K36" s="109"/>
-      <c r="L36" s="109"/>
-      <c r="M36" s="109"/>
-      <c r="N36" s="109"/>
-      <c r="O36" s="109"/>
-      <c r="P36" s="109"/>
-      <c r="Q36" s="109"/>
-      <c r="R36" s="109"/>
-      <c r="S36" s="109"/>
-      <c r="T36" s="109"/>
-      <c r="U36" s="109"/>
-      <c r="V36" s="109"/>
-      <c r="W36" s="109"/>
-      <c r="X36" s="109"/>
-      <c r="Y36" s="109"/>
-      <c r="Z36" s="109"/>
-      <c r="AA36" s="109"/>
-      <c r="AB36" s="109"/>
-      <c r="AC36" s="109"/>
-      <c r="AD36" s="109"/>
-      <c r="AE36" s="109"/>
-      <c r="AF36" s="109"/>
-      <c r="AG36" s="112"/>
+      <c r="A36" s="110"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="108"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="108"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="108"/>
+      <c r="Q36" s="108"/>
+      <c r="R36" s="108"/>
+      <c r="S36" s="108"/>
+      <c r="T36" s="108"/>
+      <c r="U36" s="108"/>
+      <c r="V36" s="108"/>
+      <c r="W36" s="108"/>
+      <c r="X36" s="108"/>
+      <c r="Y36" s="108"/>
+      <c r="Z36" s="108"/>
+      <c r="AA36" s="108"/>
+      <c r="AB36" s="108"/>
+      <c r="AC36" s="108"/>
+      <c r="AD36" s="108"/>
+      <c r="AE36" s="108"/>
+      <c r="AF36" s="108"/>
+      <c r="AG36" s="111"/>
     </row>
     <row r="37" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="74"/>
-      <c r="L37" s="74"/>
-      <c r="M37" s="74"/>
-      <c r="N37" s="74"/>
-      <c r="O37" s="74"/>
-      <c r="P37" s="74"/>
-      <c r="Q37" s="74"/>
-      <c r="R37" s="74"/>
-      <c r="S37" s="74"/>
-      <c r="T37" s="74"/>
-      <c r="U37" s="74"/>
-      <c r="V37" s="74"/>
-      <c r="W37" s="74"/>
-      <c r="X37" s="74"/>
-      <c r="Y37" s="74"/>
-      <c r="Z37" s="74"/>
-      <c r="AA37" s="74"/>
-      <c r="AB37" s="74"/>
-      <c r="AC37" s="74"/>
-      <c r="AD37" s="74"/>
-      <c r="AE37" s="74"/>
-      <c r="AF37" s="74"/>
-      <c r="AG37" s="75"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="73"/>
+      <c r="K37" s="73"/>
+      <c r="L37" s="73"/>
+      <c r="M37" s="73"/>
+      <c r="N37" s="73"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="73"/>
+      <c r="Q37" s="73"/>
+      <c r="R37" s="73"/>
+      <c r="S37" s="73"/>
+      <c r="T37" s="73"/>
+      <c r="U37" s="73"/>
+      <c r="V37" s="73"/>
+      <c r="W37" s="73"/>
+      <c r="X37" s="73"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="73"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="73"/>
+      <c r="AD37" s="73"/>
+      <c r="AE37" s="73"/>
+      <c r="AF37" s="73"/>
+      <c r="AG37" s="74"/>
     </row>
     <row r="38" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="121" t="s">
+      <c r="A38" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="123" t="s">
+      <c r="B38" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="125" t="s">
+      <c r="C38" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="125" t="s">
+      <c r="D38" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="127" t="s">
+      <c r="E38" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="113" t="s">
+      <c r="F38" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="114"/>
-      <c r="H38" s="113" t="s">
+      <c r="G38" s="113"/>
+      <c r="H38" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="I38" s="114"/>
-      <c r="J38" s="113" t="s">
+      <c r="I38" s="113"/>
+      <c r="J38" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="K38" s="114"/>
-      <c r="L38" s="113" t="s">
+      <c r="K38" s="113"/>
+      <c r="L38" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="M38" s="114"/>
-      <c r="N38" s="113" t="s">
+      <c r="M38" s="113"/>
+      <c r="N38" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="O38" s="114"/>
-      <c r="P38" s="113" t="s">
+      <c r="O38" s="113"/>
+      <c r="P38" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="Q38" s="114"/>
-      <c r="R38" s="113" t="s">
+      <c r="Q38" s="113"/>
+      <c r="R38" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="S38" s="114"/>
-      <c r="T38" s="113" t="s">
+      <c r="S38" s="113"/>
+      <c r="T38" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="U38" s="114"/>
-      <c r="V38" s="113" t="s">
+      <c r="U38" s="113"/>
+      <c r="V38" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="W38" s="114"/>
-      <c r="X38" s="113" t="s">
+      <c r="W38" s="113"/>
+      <c r="X38" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="Y38" s="114"/>
-      <c r="Z38" s="113" t="s">
+      <c r="Y38" s="113"/>
+      <c r="Z38" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="AA38" s="114"/>
-      <c r="AB38" s="113" t="s">
+      <c r="AA38" s="113"/>
+      <c r="AB38" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="AC38" s="114"/>
-      <c r="AD38" s="104" t="s">
+      <c r="AC38" s="113"/>
+      <c r="AD38" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="AE38" s="104" t="s">
+      <c r="AE38" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="AF38" s="104" t="s">
+      <c r="AF38" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AG38" s="115" t="s">
+      <c r="AG38" s="114" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:33" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="122"/>
-      <c r="B39" s="124"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="128"/>
+      <c r="A39" s="121"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="127"/>
       <c r="F39" s="13" t="s">
         <v>29</v>
       </c>
@@ -5099,10 +5141,10 @@
       <c r="AC39" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AD39" s="106"/>
-      <c r="AE39" s="106"/>
-      <c r="AF39" s="106"/>
-      <c r="AG39" s="116"/>
+      <c r="AD39" s="105"/>
+      <c r="AE39" s="105"/>
+      <c r="AF39" s="105"/>
+      <c r="AG39" s="115"/>
     </row>
     <row r="40" spans="1:33" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="49">
@@ -5129,7 +5171,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="G40" s="63" t="e">
+      <c r="G40" s="62" t="e">
         <f>F40/((($B$4/12)*G$17)+IF($B$11="Yes",($B$6/12)*G$17,$B$6/12))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7236,13 +7278,13 @@
       </c>
     </row>
     <row r="56" spans="1:33" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="70" t="s">
+      <c r="A56" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="71"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
       <c r="F56" s="52">
         <f>SUM(F40:F55)</f>
         <v>0</v>
@@ -7357,41 +7399,41 @@
       </c>
     </row>
     <row r="57" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="118" t="s">
+      <c r="A57" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="118"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="118"/>
-      <c r="H57" s="118"/>
-      <c r="I57" s="118"/>
-      <c r="J57" s="118"/>
-      <c r="K57" s="118"/>
-      <c r="L57" s="118"/>
-      <c r="M57" s="118"/>
-      <c r="N57" s="118"/>
-      <c r="O57" s="118"/>
-      <c r="P57" s="118"/>
-      <c r="Q57" s="118"/>
-      <c r="R57" s="118"/>
-      <c r="S57" s="118"/>
-      <c r="T57" s="118"/>
-      <c r="U57" s="118"/>
-      <c r="V57" s="118"/>
-      <c r="W57" s="118"/>
-      <c r="X57" s="118"/>
-      <c r="Y57" s="118"/>
-      <c r="Z57" s="118"/>
-      <c r="AA57" s="118"/>
-      <c r="AB57" s="118"/>
-      <c r="AC57" s="118"/>
-      <c r="AD57" s="118"/>
-      <c r="AE57" s="118"/>
-      <c r="AF57" s="118"/>
-      <c r="AG57" s="118"/>
+      <c r="B57" s="117"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="117"/>
+      <c r="F57" s="117"/>
+      <c r="G57" s="117"/>
+      <c r="H57" s="117"/>
+      <c r="I57" s="117"/>
+      <c r="J57" s="117"/>
+      <c r="K57" s="117"/>
+      <c r="L57" s="117"/>
+      <c r="M57" s="117"/>
+      <c r="N57" s="117"/>
+      <c r="O57" s="117"/>
+      <c r="P57" s="117"/>
+      <c r="Q57" s="117"/>
+      <c r="R57" s="117"/>
+      <c r="S57" s="117"/>
+      <c r="T57" s="117"/>
+      <c r="U57" s="117"/>
+      <c r="V57" s="117"/>
+      <c r="W57" s="117"/>
+      <c r="X57" s="117"/>
+      <c r="Y57" s="117"/>
+      <c r="Z57" s="117"/>
+      <c r="AA57" s="117"/>
+      <c r="AB57" s="117"/>
+      <c r="AC57" s="117"/>
+      <c r="AD57" s="117"/>
+      <c r="AE57" s="117"/>
+      <c r="AF57" s="117"/>
+      <c r="AG57" s="117"/>
     </row>
     <row r="58" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="59" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -7441,7 +7483,7 @@
     <row r="103" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="104" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SoohFmZD8yfuROvERdoHhjemEoomQZo5wJHYtzi+AYlgWMWMPD16OdDfsi4cV2q5Jl0KycL+SF0xpbchm3qjBQ==" saltValue="oez4cd4gME2L2NSZ3rVHvw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="w1LRbpwUVbX+QAa1taX7F3zIz0c/9UPqfB6wK2eBlA2kzqO0ZQ36bHzhzctcn8JwO58jok7wFvuK3s+D74v46Q==" saltValue="P6+xUYTAFniVJ8y8wqqcFw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="64">
     <mergeCell ref="AG16:AG18"/>
     <mergeCell ref="Z16:AA16"/>
@@ -7510,210 +7552,218 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G17">
-    <cfRule type="cellIs" dxfId="45" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="29" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="30" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="43" priority="29">
+    <cfRule type="expression" dxfId="45" priority="31">
       <formula>G34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="42" priority="41">
+    <cfRule type="expression" dxfId="44" priority="43">
       <formula>G56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="41" priority="30">
+    <cfRule type="expression" dxfId="41" priority="32">
       <formula>I34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56">
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="40" priority="44">
       <formula>I56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="cellIs" dxfId="39" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="24" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="23" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="37" priority="31">
+    <cfRule type="expression" dxfId="37" priority="33">
       <formula>K34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="expression" dxfId="36" priority="43">
+    <cfRule type="expression" dxfId="36" priority="45">
       <formula>K56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17">
-    <cfRule type="cellIs" dxfId="35" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="22" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="21" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34">
-    <cfRule type="expression" dxfId="33" priority="32">
+    <cfRule type="expression" dxfId="33" priority="34">
       <formula>M34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="expression" dxfId="32" priority="44">
+    <cfRule type="expression" dxfId="32" priority="46">
       <formula>M56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O17">
-    <cfRule type="cellIs" dxfId="31" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="19" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="20" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O34">
-    <cfRule type="expression" dxfId="29" priority="33">
+    <cfRule type="expression" dxfId="29" priority="35">
       <formula>O34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O56">
-    <cfRule type="expression" dxfId="28" priority="45">
+    <cfRule type="expression" dxfId="28" priority="47">
       <formula>O56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="27" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="18" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="17" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q34">
-    <cfRule type="expression" dxfId="25" priority="34">
+    <cfRule type="expression" dxfId="25" priority="36">
       <formula>Q34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q56">
-    <cfRule type="expression" dxfId="24" priority="46">
+    <cfRule type="expression" dxfId="24" priority="48">
       <formula>Q56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="16" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="15" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34">
-    <cfRule type="expression" dxfId="21" priority="35">
+    <cfRule type="expression" dxfId="21" priority="37">
       <formula>S34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S56">
-    <cfRule type="expression" dxfId="20" priority="47">
+    <cfRule type="expression" dxfId="20" priority="49">
       <formula>S56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U17">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34">
-    <cfRule type="expression" dxfId="17" priority="36">
+    <cfRule type="expression" dxfId="17" priority="38">
       <formula>U34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U56">
-    <cfRule type="expression" dxfId="16" priority="48">
+    <cfRule type="expression" dxfId="16" priority="50">
       <formula>U56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W17">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W34">
-    <cfRule type="expression" dxfId="13" priority="37">
+    <cfRule type="expression" dxfId="13" priority="39">
       <formula>W34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W56">
-    <cfRule type="expression" dxfId="12" priority="49">
+    <cfRule type="expression" dxfId="12" priority="51">
       <formula>W56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y17">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34">
-    <cfRule type="expression" dxfId="9" priority="38">
+    <cfRule type="expression" dxfId="9" priority="40">
       <formula>Y34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y56">
-    <cfRule type="expression" dxfId="8" priority="50">
+    <cfRule type="expression" dxfId="8" priority="52">
       <formula>Y56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA17">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA34">
-    <cfRule type="expression" dxfId="5" priority="39">
+    <cfRule type="expression" dxfId="5" priority="41">
       <formula>AA34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA56">
-    <cfRule type="expression" dxfId="4" priority="51">
+    <cfRule type="expression" dxfId="4" priority="53">
       <formula>AA56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC17">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC34">
-    <cfRule type="expression" dxfId="1" priority="40">
+    <cfRule type="expression" dxfId="1" priority="42">
       <formula>AC34&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC56">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>AC56&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
